--- a/data/trans_bre/POLIPATOLOGIA_2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_2-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 12,4</t>
+          <t>0,59; 12,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 8,41</t>
+          <t>-4,11; 9,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 8,49</t>
+          <t>-6,01; 7,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 14,99</t>
+          <t>4,36; 14,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 96,17</t>
+          <t>3,07; 102,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 50,54</t>
+          <t>-18,5; 54,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 43,65</t>
+          <t>-23,72; 39,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,2; 55,21</t>
+          <t>12,79; 53,54</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 15,46</t>
+          <t>4,34; 15,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 13,94</t>
+          <t>1,19; 13,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 7,85</t>
+          <t>-5,3; 7,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 13,16</t>
+          <t>0,6; 13,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,49; 124,86</t>
+          <t>24,49; 126,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 79,55</t>
+          <t>4,85; 75,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 41,87</t>
+          <t>-21,78; 39,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 43,59</t>
+          <t>1,7; 43,29</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 18,47</t>
+          <t>2,34; 18,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 14,23</t>
+          <t>0,55; 14,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 17,61</t>
+          <t>0,65; 17,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,34; 51,99</t>
+          <t>18,48; 54,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 87,49</t>
+          <t>9,36; 88,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 51,18</t>
+          <t>1,56; 51,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 70,22</t>
+          <t>2,26; 70,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,01; 558,23</t>
+          <t>48,87; 623,12</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 7,58</t>
+          <t>-0,66; 7,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,14</t>
+          <t>-3,57; 5,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 6,94</t>
+          <t>-1,18; 7,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 41,84</t>
+          <t>5,74; 39,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 31,49</t>
+          <t>-2,57; 32,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 19,56</t>
+          <t>-11,81; 19,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 29,06</t>
+          <t>-4,49; 31,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 125,51</t>
+          <t>15,84; 119,09</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 18,86</t>
+          <t>7,18; 18,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,81; 27,29</t>
+          <t>16,52; 27,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,97; 21,89</t>
+          <t>11,86; 21,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,02; 31,47</t>
+          <t>12,33; 31,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,35; 107,64</t>
+          <t>26,79; 102,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,64; 130,03</t>
+          <t>59,55; 130,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,56; 84,72</t>
+          <t>37,93; 83,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,68; 91,2</t>
+          <t>30,07; 88,9</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,62; 41,21</t>
+          <t>34,7; 41,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36,14; 45,94</t>
+          <t>37,3; 46,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,74; 41,94</t>
+          <t>33,65; 41,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,59; 39,18</t>
+          <t>22,31; 38,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>602,43; 2505,25</t>
+          <t>675,93; 2608,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>343,11; 1285,18</t>
+          <t>368,39; 1283,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>422,16; 1443,31</t>
+          <t>418,41; 1307,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88,78; 419,74</t>
+          <t>91,6; 396,26</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,72; 15,97</t>
+          <t>11,75; 15,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,17; 16,75</t>
+          <t>12,15; 16,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,75; 14,44</t>
+          <t>9,85; 14,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,05; 30,15</t>
+          <t>13,98; 29,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,11; 84,61</t>
+          <t>56,18; 84,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,31; 72,39</t>
+          <t>48,22; 72,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,71; 63,15</t>
+          <t>39,2; 63,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,22; 118,05</t>
+          <t>41,5; 117,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_2-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 12,67</t>
+          <t>1,32; 12,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 9,06</t>
+          <t>-4,71; 8,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 7,81</t>
+          <t>-4,33; 8,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 14,63</t>
+          <t>4,13; 14,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 102,13</t>
+          <t>4,51; 92,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 54,38</t>
+          <t>-21,14; 50,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 39,45</t>
+          <t>-17,11; 44,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,79; 53,54</t>
+          <t>11,9; 51,76</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 15,4</t>
+          <t>4,16; 15,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 13,87</t>
+          <t>0,98; 13,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 7,27</t>
+          <t>-5,56; 6,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 13,07</t>
+          <t>2,41; 13,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,49; 126,53</t>
+          <t>22,68; 129,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 75,87</t>
+          <t>3,66; 79,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 39,77</t>
+          <t>-24,09; 36,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 43,29</t>
+          <t>6,1; 46,56</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,44</t>
+          <t>19,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>143,82%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 18,72</t>
+          <t>2,61; 19,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 14,54</t>
+          <t>0,35; 14,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 17,74</t>
+          <t>-0,12; 16,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,48; 54,43</t>
+          <t>12,24; 26,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 88,83</t>
+          <t>10,88; 96,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 51,73</t>
+          <t>0,82; 52,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 70,6</t>
+          <t>-0,52; 64,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,87; 623,12</t>
+          <t>33,0; 83,36</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,13</t>
+          <t>7,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 7,78</t>
+          <t>-0,73; 7,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 5,2</t>
+          <t>-3,23; 5,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 7,65</t>
+          <t>-1,04; 7,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 39,3</t>
+          <t>3,48; 12,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 32,26</t>
+          <t>-2,65; 32,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 19,53</t>
+          <t>-11,12; 19,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 31,25</t>
+          <t>-3,85; 29,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,84; 119,09</t>
+          <t>9,61; 36,66</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,35</t>
+          <t>20,73</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 18,95</t>
+          <t>6,44; 18,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,52; 27,53</t>
+          <t>16,96; 27,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,86; 21,61</t>
+          <t>11,86; 22,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,33; 31,51</t>
+          <t>15,77; 25,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,79; 102,05</t>
+          <t>24,5; 98,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,55; 130,95</t>
+          <t>61,82; 131,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,93; 83,96</t>
+          <t>37,46; 86,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,07; 88,9</t>
+          <t>42,95; 86,51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31,83</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>208,31%</t>
+          <t>192,6%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,7; 41,53</t>
+          <t>35,07; 41,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,3; 46,38</t>
+          <t>37,05; 45,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,65; 41,84</t>
+          <t>33,8; 41,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,31; 38,54</t>
+          <t>20,71; 37,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>675,93; 2608,77</t>
+          <t>687,89; 2612,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>368,39; 1283,05</t>
+          <t>377,81; 1224,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>418,41; 1307,89</t>
+          <t>401,74; 1254,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91,6; 396,26</t>
+          <t>85,76; 388,85</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,59</t>
+          <t>13,83</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,75; 15,74</t>
+          <t>11,52; 15,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,15; 16,59</t>
+          <t>12,02; 16,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,51</t>
+          <t>10,03; 14,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,98; 29,46</t>
+          <t>11,7; 15,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,18; 84,66</t>
+          <t>55,54; 84,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,22; 72,0</t>
+          <t>47,23; 72,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,2; 63,93</t>
+          <t>39,91; 62,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41,5; 117,24</t>
+          <t>34,4; 51,1</t>
         </is>
       </c>
     </row>
